--- a/Управление IT-сервисами (Кузнецова)/План коммуникации.xlsx
+++ b/Управление IT-сервисами (Кузнецова)/План коммуникации.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TEMP\Шаблон плана коммуникаций\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rkuzu\OneDrive\Desktop\ASU\Управление IT-сервисами (Кузнецова)\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460514AA-9C78-4B82-8AD4-4530BC414A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12495"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="План_Коммуникаций" sheetId="1" r:id="rId1"/>
@@ -27,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Александр В. Южаков</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>Сообщение</t>
   </si>
@@ -163,12 +164,51 @@
   </si>
   <si>
     <t>Проект / мероприятие: _____________________________________________</t>
+  </si>
+  <si>
+    <t>Разработка модуля-интеграции с Яндекс Картами</t>
+  </si>
+  <si>
+    <t>Добрый день, коллеги! Планируется создание нового модуля для наглядного отображения маршрута пользователя. В качестве инструмента была достигнута договорённость с Яндекс, будем использовать их Яндекс.Карты. Ориентировочные сроки начала разработки - 1 июня.</t>
+  </si>
+  <si>
+    <t>Наша задача - интегрировать Яндекс Карты в программный продукт.</t>
+  </si>
+  <si>
+    <t>Для передачи конфеденциальной информации используем корпоративную почту, для общей коммуникации - беседу в мессенджере. Для созвонов/планёрок осуществлять общение через ЯндексМессенджер</t>
+  </si>
+  <si>
+    <t>Встречи внутри команды разрабоики проводить в 11 00 по МСК ежедневно. Сообщения и электронные письмы - рассылать разрешается только в рамках рабочего времени. Информацию об изменениях отсылать за две недели до их релиза.</t>
+  </si>
+  <si>
+    <t>Общий регламент: Первое сообщение - за 2 недели, напоминание - за 3 дня, итоговое подтверждение - в день релиза.</t>
+  </si>
+  <si>
+    <t>Обязательно должно быть создано техническое задание в формате docx/pdf, подписанное тех. Директором и руководителем команды разработки. Также должно быть создана вики для документации.</t>
+  </si>
+  <si>
+    <t>Для технического директора, руководителя отдела разработки - официально, но кратко (только факты и цифры). Для остальных - пошаговые инструкции, требования. Всё в рамках дружеского неформального тога</t>
+  </si>
+  <si>
+    <t>Руководитель компании - тех. директор - руководители отделов - остальные сотрудники.</t>
+  </si>
+  <si>
+    <t>Получатели письма: технический директор, руководитель отдела разработки, руководитель отдела аналитиков, ведущие разработчики(3 человека), аналитики (2 человека)</t>
+  </si>
+  <si>
+    <t>В рамках работы в корпоративном такс-трекере должен быть создан раздел FAQ(частые вопросы), в котором будут описаны ответы на часто задаваемые вопросы.</t>
+  </si>
+  <si>
+    <t>для достижения поставленной цели потребуется около 1000 человеко-часов разработчиков, около 400 человеко-часов тестировщиков и системных  аналитиков.</t>
+  </si>
+  <si>
+    <t>для сообщений в корпоративном мессенджере: адресат письма должен поставить реакцию, подтверждающую получение информации. Также предполагается общение в комментариях в таск-трекере по конкретным задачам.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -570,7 +610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="12.75" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -593,7 +633,9 @@
       <c r="A2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
@@ -612,7 +654,7 @@
       </c>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -622,7 +664,9 @@
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -635,10 +679,12 @@
       <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -648,7 +694,9 @@
       <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -661,10 +709,12 @@
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="E7" s="7"/>
     </row>
-    <row r="8" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -674,7 +724,9 @@
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5" ht="67.5" x14ac:dyDescent="0.2">
@@ -687,7 +739,9 @@
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="78.75" x14ac:dyDescent="0.2">
@@ -700,7 +754,9 @@
       <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" ht="56.25" x14ac:dyDescent="0.2">
@@ -713,7 +769,9 @@
       <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.2">
@@ -726,7 +784,9 @@
       <c r="C12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="78.75" x14ac:dyDescent="0.2">
@@ -739,7 +799,9 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -752,10 +814,12 @@
       <c r="C14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -765,11 +829,13 @@
       <c r="C15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="E15" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3"/>
+  <autoFilter ref="A3:E3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>

--- a/Управление IT-сервисами (Кузнецова)/План коммуникации.xlsx
+++ b/Управление IT-сервисами (Кузнецова)/План коммуникации.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rkuzu\OneDrive\Desktop\ASU\Управление IT-сервисами (Кузнецова)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460514AA-9C78-4B82-8AD4-4530BC414A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3744F813-BD27-4150-8094-1514D815E037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="98">
   <si>
     <t>Сообщение</t>
   </si>
@@ -203,6 +203,154 @@
   </si>
   <si>
     <t>для сообщений в корпоративном мессенджере: адресат письма должен поставить реакцию, подтверждающую получение информации. Также предполагается общение в комментариях в таск-трекере по конкретным задачам.</t>
+  </si>
+  <si>
+    <t>Проведение code review и контроль качества кода</t>
+  </si>
+  <si>
+    <t>Наша задача - снижение количества ошибок перед релизом.</t>
+  </si>
+  <si>
+    <t>Получатели письма: руководитель отдела разработки, руководитель отдела аналитиков, команда разработчиков</t>
+  </si>
+  <si>
+    <t>Для руководителя отдела разработки - официально, но кратко (только факты и цифры). Для остальных - неформальный технический стиль с примерами и рекомендациями</t>
+  </si>
+  <si>
+    <t>Проверка pull request - не позднее 24 часов после создания
+Критические замечания - сразу после обнаружения
+Повторная проверка - после исправлений</t>
+  </si>
+  <si>
+    <t>Постоянно в течение всей разработки.</t>
+  </si>
+  <si>
+    <t>Все комментарии указывать в коммитах и при git merge</t>
+  </si>
+  <si>
+    <t>Разработчик должен ответить на комментарии,
+исправить замечания, повторно отправить код на проверку.</t>
+  </si>
+  <si>
+    <t>руководитель отдела - ведущие разработчики - остальные разработчики.</t>
+  </si>
+  <si>
+    <t>Около 120 человеко-часов ведущих разработчиков</t>
+  </si>
+  <si>
+    <t>среднее время code review, а также количество багов после релиза</t>
+  </si>
+  <si>
+    <t>Добрый день, коллеги! В рамках разработки модуля интеграции с Яндекс.Картами вводится обязательный code review для всех задач, связанных с  интеграцией API.</t>
+  </si>
+  <si>
+    <t>Добрый день, коллеги! После завершения основных этапов разработки начинается этап функционального и интеграционного тестирования модуля Яндекс.Карт. Необходимо проверить корректность отображения маршрутов.</t>
+  </si>
+  <si>
+    <t>Задача - проверка корректности отображения маршрутов</t>
+  </si>
+  <si>
+    <t>Для всех - формальный технический стиль с детальным описанием ошибок и шагов воспроизведения</t>
+  </si>
+  <si>
+    <t>Получатели письма: руководитель отдела разработки, руководитель отдела аналитиков, тестировщики</t>
+  </si>
+  <si>
+    <t>Тестирование начинается после завершения MVP и продолжается до релиза.</t>
+  </si>
+  <si>
+    <t>Регрессионные тесты - перед релизом. Юнит-тесты - постоянно</t>
+  </si>
+  <si>
+    <t>необходимо создавать еженедельные отчёты об ошибках</t>
+  </si>
+  <si>
+    <t>руководитель отдела разработки - тестировщики</t>
+  </si>
+  <si>
+    <t>Тестировщики должны подтвердить получение бага, отобразить ошибку в отчете и направить информацию руководителю отдела.</t>
+  </si>
+  <si>
+    <t>Количество найденных багов, среднее время исправления ошибки</t>
+  </si>
+  <si>
+    <t>Около 400 человеко-часов тестировщиков</t>
+  </si>
+  <si>
+    <t>Тестировка и обработка багов</t>
+  </si>
+  <si>
+    <t>Добрый день, коллеги! Планируется демонстрация промежуточной версии модуля Яндекс.Карт для получения обратной связи по интерфейсу, маршрутам и пользовательскому сценарию.</t>
+  </si>
+  <si>
+    <t>Наша задача - продемонстрировать построение маршрута, а также дополнительный функционал MVP</t>
+  </si>
+  <si>
+    <t>Для всех - официальный, но понятный для нетехнической аудитории</t>
+  </si>
+  <si>
+    <t>После завершения MVP</t>
+  </si>
+  <si>
+    <t>Не более двух демонстраций за проект</t>
+  </si>
+  <si>
+    <t>Презентация, прототип, RoadMap, список реализованных функций</t>
+  </si>
+  <si>
+    <t>Получатели письма: Генеральный директор, технический директор, руководители отделов аналитики и разработки</t>
+  </si>
+  <si>
+    <t>Генеральный директор - тех. директор - руководители проектов</t>
+  </si>
+  <si>
+    <t>В ответ ожидаем получений замечаний/предложений, а также согласование дальнейшей разработки</t>
+  </si>
+  <si>
+    <t>Количество замечаний, количество изменений после демонстрации</t>
+  </si>
+  <si>
+    <t>Около 40 человеко-часов</t>
+  </si>
+  <si>
+    <t>Финальный релиз</t>
+  </si>
+  <si>
+    <t>Демонстрация генеральному директору</t>
+  </si>
+  <si>
+    <t>Добрый день, коллеги!
+Сообщаем о завершении разработки и выпуске модуля интеграции с Яндекс.Картами.</t>
+  </si>
+  <si>
+    <t>Наша задача - провести финальный релиз. Дата 15 сентября.</t>
+  </si>
+  <si>
+    <t>все сотрудники проекта.</t>
+  </si>
+  <si>
+    <t>Официальный, строгий с четким указанием дат.</t>
+  </si>
+  <si>
+    <t>Первое сообщение - за 2 недели, напоминание - за 3 дня, итоговое подтверждение - в день релиза.</t>
+  </si>
+  <si>
+    <t>Первое сообщение - в понедельник утром за две недели до релиза</t>
+  </si>
+  <si>
+    <t>Около 80 человеко-часов разработчиков</t>
+  </si>
+  <si>
+    <t>Количество успешно обработных запросов, количество обращений в поддержку.</t>
+  </si>
+  <si>
+    <t>Сотрудники должны подтвердить ознакомление, сообщить о найденных проблемах.</t>
+  </si>
+  <si>
+    <t>Технический директор - руководители отделов - остальные сотрудников</t>
+  </si>
+  <si>
+    <t>Технический директор, руководители отделов, остальные сотрудников</t>
   </si>
 </sst>
 </file>
@@ -274,7 +422,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -297,39 +445,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,231 +813,380 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="12.75" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1" outlineLevel="1"/>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="45.85546875" customWidth="1"/>
-    <col min="5" max="5" width="38.7109375" customWidth="1"/>
+    <col min="4" max="4" width="53.7109375" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" customWidth="1"/>
+    <col min="6" max="6" width="54.5703125" customWidth="1"/>
+    <col min="7" max="7" width="32.140625" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
+      <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:5" s="5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="E2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" ht="152.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="E5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="67.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="78.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="E9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="56.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="E10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="56.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="90" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="78.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:E3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="D8:H8"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
